--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487737_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487737_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.073</v>
+        <v>1.8262</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5656</v>
+        <v>1.2643</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5074</v>
+        <v>0.5619</v>
       </c>
       <c r="G2" t="n">
         <v>-1.8621</v>
@@ -610,13 +610,13 @@
         <v>1.3582</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3053</v>
+        <v>1.0585</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1366</v>
+        <v>0.8353</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1687</v>
+        <v>0.2232</v>
       </c>
       <c r="V2" t="n">
         <v>1.2716</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1096</v>
+        <v>1.7825</v>
       </c>
       <c r="E3" t="n">
         <v>3.1862</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0766</v>
+        <v>-1.4037</v>
       </c>
       <c r="G3" t="n">
         <v>1.4418</v>
@@ -688,13 +688,13 @@
         <v>0.3881</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5036</v>
+        <v>1.1765</v>
       </c>
       <c r="T3" t="n">
         <v>0.2804</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2232</v>
+        <v>0.8962</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2239</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8188</v>
+        <v>0.8154</v>
       </c>
       <c r="E4" t="n">
-        <v>2.674</v>
+        <v>2.5344</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.8552</v>
+        <v>-1.7189</v>
       </c>
       <c r="G4" t="n">
         <v>0.5376</v>
@@ -766,13 +766,13 @@
         <v>0.194</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1155</v>
+        <v>0.1122</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0617</v>
+        <v>-0.078</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0538</v>
+        <v>0.1901</v>
       </c>
       <c r="V4" t="n">
         <v>0.9418</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4862</v>
+        <v>0.4867</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3315</v>
+        <v>-0.0312</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8177</v>
+        <v>0.5179</v>
       </c>
       <c r="G5" t="n">
         <v>-2.1307</v>
@@ -844,13 +844,13 @@
         <v>1.7463</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9273</v>
+        <v>0.9278</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1436</v>
+        <v>0.1567</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0709</v>
+        <v>0.7711</v>
       </c>
       <c r="V5" t="n">
         <v>1.8836</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1718</v>
+        <v>0.1707</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2748</v>
+        <v>1.5355</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4465</v>
+        <v>-1.3648</v>
       </c>
       <c r="G6" t="n">
         <v>2.9985</v>
@@ -922,13 +922,13 @@
         <v>0.7761</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7822</v>
+        <v>-0.4397</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3634</v>
+        <v>-0.1026</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4188</v>
+        <v>-0.337</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2239</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5878</v>
+        <v>-0.0417</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1409</v>
+        <v>-0.5403</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5531</v>
+        <v>0.4986</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5145</v>
@@ -1000,13 +1000,13 @@
         <v>0.3881</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5088</v>
+        <v>1.0548</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2299</v>
+        <v>0.3707</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7387</v>
+        <v>0.6842</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1037</v>
+        <v>-0.2217</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0964</v>
+        <v>-0.5959</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0073</v>
+        <v>0.3742</v>
       </c>
       <c r="G8" t="n">
         <v>0.1723</v>
@@ -1078,13 +1078,13 @@
         <v>0.3881</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4118</v>
+        <v>0.4702</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.0323</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1209</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2821</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8304</v>
+        <v>-2.2876</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5131</v>
+        <v>-1.0521</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3173</v>
+        <v>-1.2355</v>
       </c>
       <c r="G9" t="n">
         <v>-3.2528</v>
@@ -1156,13 +1156,13 @@
         <v>1.3582</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.085</v>
+        <v>-0.5423</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0655</v>
+        <v>-0.6046</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0195</v>
+        <v>0.0623</v>
       </c>
       <c r="V9" t="n">
         <v>3.0597</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4802</v>
+        <v>-3.0653</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7876</v>
+        <v>-0.727</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6926</v>
+        <v>-2.3383</v>
       </c>
       <c r="G10" t="n">
         <v>-2.645</v>
@@ -1234,13 +1234,13 @@
         <v>1.5523</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5994</v>
+        <v>-0.1845</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3982</v>
+        <v>-0.3376</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2012</v>
+        <v>0.1531</v>
       </c>
       <c r="V10" t="n">
         <v>-1.788</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0323</v>
+        <v>-5.8811</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9994</v>
+        <v>0.5595</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.0317</v>
+        <v>-6.4405</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4483</v>
@@ -1312,13 +1312,13 @@
         <v>0.5821</v>
       </c>
       <c r="S11" t="n">
-        <v>1.522</v>
+        <v>0.6732</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4508</v>
+        <v>0.0109</v>
       </c>
       <c r="U11" t="n">
-        <v>1.0711</v>
+        <v>0.6623</v>
       </c>
       <c r="V11" t="n">
         <v>-2.7776</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.7186</v>
+        <v>-6.4159</v>
       </c>
       <c r="E12" t="n">
-        <v>5.830499999999998</v>
+        <v>6.133399999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-12.549</v>
+        <v>-12.5491</v>
       </c>
       <c r="G12" t="n">
         <v>-6.703200000000001</v>
@@ -1390,13 +1390,13 @@
         <v>8.731500000000002</v>
       </c>
       <c r="S12" t="n">
-        <v>4.0041</v>
+        <v>4.306700000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1960999999999995</v>
+        <v>0.4988999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>3.8078</v>
+        <v>3.808</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1388000000000003</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.9397</v>
+        <v>7.4308</v>
       </c>
       <c r="E13" t="n">
-        <v>7.4568</v>
+        <v>6.9563</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4829</v>
+        <v>0.4745</v>
       </c>
       <c r="G13" t="n">
         <v>7.0914</v>
@@ -1468,13 +1468,13 @@
         <v>1.3582</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2663</v>
+        <v>0.7574</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4262</v>
+        <v>-0.0743</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8401</v>
+        <v>0.8317</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6119</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. DIAZ MONTERO</t>
+          <t>J. ATIENZA PEREA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3991</v>
+        <v>4.7534</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5209</v>
+        <v>3.2634</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1218</v>
+        <v>1.49</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5751</v>
+        <v>1.9444</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2714</v>
+        <v>-1.5942</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6963</v>
+        <v>3.5386</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7742</v>
+        <v>2.7144</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7641</v>
+        <v>-1.1246</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0101</v>
+        <v>3.8389</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.199</v>
+        <v>-0.77</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4927</v>
+        <v>-0.4696</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7063</v>
+        <v>-0.3004</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7761</v>
+        <v>1.7463</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1642</v>
+        <v>-0.194</v>
       </c>
       <c r="R14" t="n">
         <v>1.9403</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3044</v>
+        <v>-0.773</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6651</v>
+        <v>-1.0927</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3608</v>
+        <v>0.3197</v>
       </c>
       <c r="V14" t="n">
-        <v>2.3522</v>
+        <v>1.8358</v>
       </c>
       <c r="W14" t="n">
-        <v>3.5761</v>
+        <v>1.8358</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. ATIENZA PEREA</t>
+          <t>G. DIAZ MONTERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7802</v>
+        <v>4.6726</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9631</v>
+        <v>4.7211</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8171</v>
+        <v>-0.0485</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9444</v>
+        <v>1.5751</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.5942</v>
+        <v>2.2714</v>
       </c>
       <c r="I15" t="n">
-        <v>3.5386</v>
+        <v>-0.6963</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7144</v>
+        <v>2.7742</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.1246</v>
+        <v>2.7641</v>
       </c>
       <c r="L15" t="n">
-        <v>3.8389</v>
+        <v>0.0101</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.77</v>
+        <v>-1.199</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4696</v>
+        <v>-0.4927</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3004</v>
+        <v>-0.7063</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7463</v>
+        <v>0.7761</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.194</v>
+        <v>-1.1642</v>
       </c>
       <c r="R15" t="n">
         <v>1.9403</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.7463</v>
+        <v>-0.0308</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.393</v>
+        <v>-0.4649</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3533</v>
+        <v>0.4341</v>
       </c>
       <c r="V15" t="n">
-        <v>1.8358</v>
+        <v>2.3522</v>
       </c>
       <c r="W15" t="n">
-        <v>1.8358</v>
+        <v>3.5761</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. MAIGA</t>
+          <t>G. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5907</v>
+        <v>0.841</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3435</v>
+        <v>1.9152</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2472</v>
+        <v>-1.0742</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1549</v>
+        <v>1.1317</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7522</v>
+        <v>0.7481</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.3837</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3664</v>
+        <v>2.1631</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2019</v>
+        <v>1.3512</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1646</v>
+        <v>0.8119</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5214</v>
+        <v>-1.0313</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9540999999999999</v>
+        <v>-0.6031</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5673</v>
+        <v>-0.4282</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7761</v>
+        <v>0.3881</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1642</v>
+        <v>-0.9702</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9403</v>
+        <v>1.3582</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6292</v>
+        <v>-0.9609</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4229</v>
+        <v>-0.7837</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0521</v>
+        <v>-0.1772</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6597</v>
+        <v>0.2821</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5642</v>
+        <v>1.506</v>
       </c>
       <c r="X16" t="n">
         <v>-1.2239</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. LARDIES GUILLEN</t>
+          <t>N. MAIGA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4683</v>
+        <v>0.5128</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2155</v>
+        <v>0.5437</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7471</v>
+        <v>-0.031</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1317</v>
+        <v>-0.1549</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7481</v>
+        <v>-0.7522</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3837</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1631</v>
+        <v>1.3664</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3512</v>
+        <v>0.2019</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8119</v>
+        <v>1.1646</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0313</v>
+        <v>-1.5214</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6031</v>
+        <v>-0.9540999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4282</v>
+        <v>-0.5673</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3881</v>
+        <v>0.7761</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9702</v>
+        <v>-1.1642</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3582</v>
+        <v>1.9403</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3336</v>
+        <v>0.5513</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4834</v>
+        <v>-0.2227</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8501</v>
+        <v>0.7739</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2821</v>
+        <v>-0.6597</v>
       </c>
       <c r="W17" t="n">
-        <v>1.506</v>
+        <v>0.5642</v>
       </c>
       <c r="X17" t="n">
         <v>-1.2239</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1227</v>
+        <v>-0.0682</v>
       </c>
       <c r="E18" t="n">
         <v>-0.0805</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0421</v>
+        <v>0.0124</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2319</v>
@@ -1858,13 +1858,13 @@
         <v>0.194</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0848</v>
+        <v>-0.0303</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1211</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0363</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4898</v>
+        <v>-2.4842</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3945</v>
+        <v>-1.7949</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0952</v>
+        <v>-0.6892</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6456</v>
@@ -1936,13 +1936,13 @@
         <v>2.1344</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2905</v>
+        <v>-0.2849</v>
       </c>
       <c r="T19" t="n">
-        <v>0.06279999999999999</v>
+        <v>-0.3376</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3533</v>
+        <v>0.0527</v>
       </c>
       <c r="V19" t="n">
         <v>-1.5537</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0883</v>
+        <v>-2.57</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1963</v>
+        <v>-1.896</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.892</v>
+        <v>-0.6739000000000001</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6786</v>
@@ -2014,13 +2014,13 @@
         <v>0.9702</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1276</v>
+        <v>-0.6093</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6057</v>
+        <v>-0.3054</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.522</v>
+        <v>-0.3039</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2821</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.7587</v>
+        <v>-4.3678</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2793</v>
+        <v>-1.0791</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.4794</v>
+        <v>-3.2886</v>
       </c>
       <c r="G21" t="n">
         <v>-2.3285</v>
@@ -2092,13 +2092,13 @@
         <v>0.7761</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0123</v>
+        <v>-0.6214</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6057</v>
+        <v>-0.4055</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4067</v>
+        <v>-0.2159</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2239</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>6.7185</v>
+        <v>8.720400000000001</v>
       </c>
       <c r="E22" t="n">
         <v>12.5492</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.8304</v>
+        <v>-3.8285</v>
       </c>
       <c r="G22" t="n">
         <v>6.703099999999999</v>
@@ -2146,10 +2146,10 @@
         <v>16.1483</v>
       </c>
       <c r="K22" t="n">
-        <v>9.252300000000002</v>
+        <v>9.2523</v>
       </c>
       <c r="L22" t="n">
-        <v>6.896199999999999</v>
+        <v>6.8962</v>
       </c>
       <c r="M22" t="n">
         <v>-9.4452</v>
@@ -2170,16 +2170,16 @@
         <v>12.612</v>
       </c>
       <c r="S22" t="n">
-        <v>-4.004</v>
+        <v>-2.0019</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.807900000000001</v>
+        <v>-3.8079</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1960999999999999</v>
+        <v>1.8059</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1388000000000003</v>
+        <v>0.1387999999999998</v>
       </c>
       <c r="W22" t="n">
         <v>8.940300000000001</v>
